--- a/data/palpites/BOLAO2026_VIRGILIO.xlsx
+++ b/data/palpites/BOLAO2026_VIRGILIO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9528F0BAC16452F1/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\bolao2026\data\palpites\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A496032-D0EC-4CF6-B664-05E7DE280EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11607F8-BD3D-4217-8CD8-798EF2D0BC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{2FAB9762-9002-4221-90DC-1459ADDAB04F}"/>
+    <workbookView xWindow="750" yWindow="2655" windowWidth="18945" windowHeight="12165" activeTab="1" xr2:uid="{2FAB9762-9002-4221-90DC-1459ADDAB04F}"/>
   </bookViews>
   <sheets>
     <sheet name="GRUPOS" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="135">
   <si>
     <r>
       <rPr>
@@ -1728,16 +1728,43 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1765,37 +1792,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9123,9 +9123,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9163,7 +9163,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9269,7 +9269,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9411,7 +9411,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -9481,33 +9481,33 @@
     <row r="2" spans="1:30" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="140" t="s">
+      <c r="C2" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="140"/>
-      <c r="P2" s="140"/>
-      <c r="Q2" s="140"/>
-      <c r="R2" s="140"/>
-      <c r="S2" s="140"/>
-      <c r="T2" s="140"/>
-      <c r="U2" s="140"/>
-      <c r="V2" s="140"/>
-      <c r="W2" s="140"/>
-      <c r="X2" s="140"/>
-      <c r="Y2" s="140"/>
-      <c r="Z2" s="140"/>
-      <c r="AA2" s="140"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="4"/>
@@ -9579,35 +9579,35 @@
     <row r="5" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="137" t="s">
+      <c r="C5" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="138"/>
-      <c r="E5" s="138"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="138"/>
-      <c r="J5" s="138"/>
-      <c r="K5" s="138"/>
-      <c r="L5" s="138"/>
-      <c r="M5" s="138"/>
-      <c r="N5" s="139"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="127"/>
+      <c r="M5" s="127"/>
+      <c r="N5" s="128"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="137" t="s">
+      <c r="P5" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="Q5" s="138"/>
-      <c r="R5" s="138"/>
-      <c r="S5" s="138"/>
-      <c r="T5" s="138"/>
-      <c r="U5" s="138"/>
-      <c r="V5" s="138"/>
-      <c r="W5" s="138"/>
-      <c r="X5" s="138"/>
-      <c r="Y5" s="138"/>
-      <c r="Z5" s="138"/>
-      <c r="AA5" s="139"/>
+      <c r="Q5" s="127"/>
+      <c r="R5" s="127"/>
+      <c r="S5" s="127"/>
+      <c r="T5" s="127"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="127"/>
+      <c r="W5" s="127"/>
+      <c r="X5" s="127"/>
+      <c r="Y5" s="127"/>
+      <c r="Z5" s="127"/>
+      <c r="AA5" s="128"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="4"/>
@@ -9989,35 +9989,35 @@
     <row r="13" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="137" t="s">
+      <c r="C13" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="138"/>
-      <c r="I13" s="138"/>
-      <c r="J13" s="138"/>
-      <c r="K13" s="138"/>
-      <c r="L13" s="138"/>
-      <c r="M13" s="138"/>
-      <c r="N13" s="139"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="127"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="128"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="137" t="s">
+      <c r="P13" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="Q13" s="138"/>
-      <c r="R13" s="138"/>
-      <c r="S13" s="138"/>
-      <c r="T13" s="138"/>
-      <c r="U13" s="138"/>
-      <c r="V13" s="138"/>
-      <c r="W13" s="138"/>
-      <c r="X13" s="138"/>
-      <c r="Y13" s="138"/>
-      <c r="Z13" s="138"/>
-      <c r="AA13" s="139"/>
+      <c r="Q13" s="127"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="127"/>
+      <c r="T13" s="127"/>
+      <c r="U13" s="127"/>
+      <c r="V13" s="127"/>
+      <c r="W13" s="127"/>
+      <c r="X13" s="127"/>
+      <c r="Y13" s="127"/>
+      <c r="Z13" s="127"/>
+      <c r="AA13" s="128"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="4"/>
@@ -10396,35 +10396,35 @@
     <row r="21" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="137" t="s">
+      <c r="C21" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="138"/>
-      <c r="E21" s="138"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="138"/>
-      <c r="I21" s="138"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="138"/>
-      <c r="M21" s="138"/>
-      <c r="N21" s="139"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="127"/>
+      <c r="G21" s="127"/>
+      <c r="H21" s="127"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="127"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="127"/>
+      <c r="N21" s="128"/>
       <c r="O21" s="1"/>
-      <c r="P21" s="137" t="s">
+      <c r="P21" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="Q21" s="138"/>
-      <c r="R21" s="138"/>
-      <c r="S21" s="138"/>
-      <c r="T21" s="138"/>
-      <c r="U21" s="138"/>
-      <c r="V21" s="138"/>
-      <c r="W21" s="138"/>
-      <c r="X21" s="138"/>
-      <c r="Y21" s="138"/>
-      <c r="Z21" s="138"/>
-      <c r="AA21" s="139"/>
+      <c r="Q21" s="127"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="127"/>
+      <c r="U21" s="127"/>
+      <c r="V21" s="127"/>
+      <c r="W21" s="127"/>
+      <c r="X21" s="127"/>
+      <c r="Y21" s="127"/>
+      <c r="Z21" s="127"/>
+      <c r="AA21" s="128"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="4"/>
@@ -10803,35 +10803,35 @@
     <row r="29" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="137" t="s">
+      <c r="C29" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="138"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="138"/>
-      <c r="I29" s="138"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="138"/>
-      <c r="L29" s="138"/>
-      <c r="M29" s="138"/>
-      <c r="N29" s="139"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="127"/>
+      <c r="G29" s="127"/>
+      <c r="H29" s="127"/>
+      <c r="I29" s="127"/>
+      <c r="J29" s="127"/>
+      <c r="K29" s="127"/>
+      <c r="L29" s="127"/>
+      <c r="M29" s="127"/>
+      <c r="N29" s="128"/>
       <c r="O29" s="1"/>
-      <c r="P29" s="137" t="s">
+      <c r="P29" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="Q29" s="138"/>
-      <c r="R29" s="138"/>
-      <c r="S29" s="138"/>
-      <c r="T29" s="138"/>
-      <c r="U29" s="138"/>
-      <c r="V29" s="138"/>
-      <c r="W29" s="138"/>
-      <c r="X29" s="138"/>
-      <c r="Y29" s="138"/>
-      <c r="Z29" s="138"/>
-      <c r="AA29" s="139"/>
+      <c r="Q29" s="127"/>
+      <c r="R29" s="127"/>
+      <c r="S29" s="127"/>
+      <c r="T29" s="127"/>
+      <c r="U29" s="127"/>
+      <c r="V29" s="127"/>
+      <c r="W29" s="127"/>
+      <c r="X29" s="127"/>
+      <c r="Y29" s="127"/>
+      <c r="Z29" s="127"/>
+      <c r="AA29" s="128"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="4"/>
@@ -11207,35 +11207,35 @@
     <row r="37" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="137" t="s">
+      <c r="C37" s="126" t="s">
         <v>78</v>
       </c>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
-      <c r="G37" s="138"/>
-      <c r="H37" s="138"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="138"/>
-      <c r="K37" s="138"/>
-      <c r="L37" s="138"/>
-      <c r="M37" s="138"/>
-      <c r="N37" s="139"/>
+      <c r="D37" s="127"/>
+      <c r="E37" s="127"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="127"/>
+      <c r="H37" s="127"/>
+      <c r="I37" s="127"/>
+      <c r="J37" s="127"/>
+      <c r="K37" s="127"/>
+      <c r="L37" s="127"/>
+      <c r="M37" s="127"/>
+      <c r="N37" s="128"/>
       <c r="O37" s="1"/>
-      <c r="P37" s="137" t="s">
+      <c r="P37" s="126" t="s">
         <v>79</v>
       </c>
-      <c r="Q37" s="138"/>
-      <c r="R37" s="138"/>
-      <c r="S37" s="138"/>
-      <c r="T37" s="138"/>
-      <c r="U37" s="138"/>
-      <c r="V37" s="138"/>
-      <c r="W37" s="138"/>
-      <c r="X37" s="138"/>
-      <c r="Y37" s="138"/>
-      <c r="Z37" s="138"/>
-      <c r="AA37" s="139"/>
+      <c r="Q37" s="127"/>
+      <c r="R37" s="127"/>
+      <c r="S37" s="127"/>
+      <c r="T37" s="127"/>
+      <c r="U37" s="127"/>
+      <c r="V37" s="127"/>
+      <c r="W37" s="127"/>
+      <c r="X37" s="127"/>
+      <c r="Y37" s="127"/>
+      <c r="Z37" s="127"/>
+      <c r="AA37" s="128"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="4"/>
@@ -11614,35 +11614,35 @@
     <row r="45" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-      <c r="C45" s="137" t="s">
+      <c r="C45" s="126" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="138"/>
-      <c r="E45" s="138"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="138"/>
-      <c r="H45" s="138"/>
-      <c r="I45" s="138"/>
-      <c r="J45" s="138"/>
-      <c r="K45" s="138"/>
-      <c r="L45" s="138"/>
-      <c r="M45" s="138"/>
-      <c r="N45" s="139"/>
+      <c r="D45" s="127"/>
+      <c r="E45" s="127"/>
+      <c r="F45" s="127"/>
+      <c r="G45" s="127"/>
+      <c r="H45" s="127"/>
+      <c r="I45" s="127"/>
+      <c r="J45" s="127"/>
+      <c r="K45" s="127"/>
+      <c r="L45" s="127"/>
+      <c r="M45" s="127"/>
+      <c r="N45" s="128"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="137" t="s">
+      <c r="P45" s="126" t="s">
         <v>98</v>
       </c>
-      <c r="Q45" s="138"/>
-      <c r="R45" s="138"/>
-      <c r="S45" s="138"/>
-      <c r="T45" s="138"/>
-      <c r="U45" s="138"/>
-      <c r="V45" s="138"/>
-      <c r="W45" s="138"/>
-      <c r="X45" s="138"/>
-      <c r="Y45" s="138"/>
-      <c r="Z45" s="138"/>
-      <c r="AA45" s="139"/>
+      <c r="Q45" s="127"/>
+      <c r="R45" s="127"/>
+      <c r="S45" s="127"/>
+      <c r="T45" s="127"/>
+      <c r="U45" s="127"/>
+      <c r="V45" s="127"/>
+      <c r="W45" s="127"/>
+      <c r="X45" s="127"/>
+      <c r="Y45" s="127"/>
+      <c r="Z45" s="127"/>
+      <c r="AA45" s="128"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="4"/>
@@ -12084,12 +12084,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C29:N29"/>
-    <mergeCell ref="P29:AA29"/>
-    <mergeCell ref="C37:N37"/>
-    <mergeCell ref="P37:AA37"/>
-    <mergeCell ref="C45:N45"/>
-    <mergeCell ref="P45:AA45"/>
     <mergeCell ref="C21:N21"/>
     <mergeCell ref="P21:AA21"/>
     <mergeCell ref="C2:AA2"/>
@@ -12097,6 +12091,12 @@
     <mergeCell ref="P5:AA5"/>
     <mergeCell ref="C13:N13"/>
     <mergeCell ref="P13:AA13"/>
+    <mergeCell ref="C29:N29"/>
+    <mergeCell ref="P29:AA29"/>
+    <mergeCell ref="C37:N37"/>
+    <mergeCell ref="P37:AA37"/>
+    <mergeCell ref="C45:N45"/>
+    <mergeCell ref="P45:AA45"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -12149,22 +12149,22 @@
     </row>
     <row r="3" spans="1:26" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A3" s="32"/>
-      <c r="B3" s="144" t="s">
+      <c r="B3" s="136" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="144"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="144"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="144"/>
-      <c r="M3" s="144"/>
-      <c r="N3" s="144"/>
-      <c r="O3" s="144"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="121"/>
       <c r="R3" s="121"/>
@@ -12215,28 +12215,28 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="32"/>
-      <c r="B6" s="141" t="s">
+      <c r="B6" s="134" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="141"/>
-      <c r="D6" s="141"/>
-      <c r="E6" s="142" t="s">
+      <c r="C6" s="134"/>
+      <c r="D6" s="134"/>
+      <c r="E6" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="142"/>
-      <c r="G6" s="142"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
-      <c r="J6" s="141" t="s">
+      <c r="J6" s="134" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="141"/>
-      <c r="L6" s="141"/>
-      <c r="M6" s="142" t="s">
+      <c r="K6" s="134"/>
+      <c r="L6" s="134"/>
+      <c r="M6" s="130" t="s">
         <v>103</v>
       </c>
-      <c r="N6" s="142"/>
-      <c r="O6" s="142"/>
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
       <c r="P6" s="32"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -12263,16 +12263,16 @@
       <c r="C8" s="123"/>
       <c r="D8" s="123"/>
       <c r="E8" s="32"/>
-      <c r="F8" s="141" t="s">
+      <c r="F8" s="134" t="s">
         <v>128</v>
       </c>
-      <c r="G8" s="141"/>
-      <c r="H8" s="141"/>
-      <c r="I8" s="142" t="s">
+      <c r="G8" s="134"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="J8" s="142"/>
-      <c r="K8" s="142"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="130"/>
       <c r="L8" s="32"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
@@ -12318,32 +12318,32 @@
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="32"/>
       <c r="B11" s="32"/>
-      <c r="C11" s="143" t="s">
+      <c r="C11" s="135" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="143"/>
-      <c r="E11" s="143"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
       <c r="K11" s="32"/>
-      <c r="L11" s="143" t="s">
+      <c r="L11" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="M11" s="143"/>
-      <c r="N11" s="143"/>
+      <c r="M11" s="135"/>
+      <c r="N11" s="135"/>
       <c r="O11" s="32"/>
       <c r="P11" s="32"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="32"/>
       <c r="B12" s="32"/>
-      <c r="C12" s="146" t="s">
+      <c r="C12" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="147"/>
+      <c r="D12" s="133"/>
       <c r="E12" s="124"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
@@ -12351,23 +12351,21 @@
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
-      <c r="L12" s="146" t="s">
+      <c r="L12" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="M12" s="147"/>
-      <c r="N12" s="124" t="s">
-        <v>5</v>
-      </c>
+      <c r="M12" s="133"/>
+      <c r="N12" s="124"/>
       <c r="O12" s="32"/>
       <c r="P12" s="32"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="32"/>
       <c r="B13" s="32"/>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="145"/>
+      <c r="D13" s="131"/>
       <c r="E13" s="125"/>
       <c r="F13" s="32"/>
       <c r="G13" s="32"/>
@@ -12375,10 +12373,10 @@
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
-      <c r="L13" s="142" t="s">
+      <c r="L13" s="130" t="s">
         <v>131</v>
       </c>
-      <c r="M13" s="145"/>
+      <c r="M13" s="131"/>
       <c r="N13" s="125"/>
       <c r="O13" s="32"/>
       <c r="P13" s="32"/>
@@ -12386,10 +12384,10 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="32"/>
       <c r="B14" s="32"/>
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="145"/>
+      <c r="D14" s="131"/>
       <c r="E14" s="125"/>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -12397,10 +12395,10 @@
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
       <c r="K14" s="32"/>
-      <c r="L14" s="142" t="s">
+      <c r="L14" s="130" t="s">
         <v>29</v>
       </c>
-      <c r="M14" s="145"/>
+      <c r="M14" s="131"/>
       <c r="N14" s="125"/>
       <c r="O14" s="32"/>
       <c r="P14" s="32"/>
@@ -12408,10 +12406,10 @@
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="32"/>
       <c r="B15" s="32"/>
-      <c r="C15" s="142" t="s">
+      <c r="C15" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="145"/>
+      <c r="D15" s="131"/>
       <c r="E15" s="125" t="s">
         <v>134</v>
       </c>
@@ -12421,10 +12419,10 @@
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
       <c r="K15" s="32"/>
-      <c r="L15" s="142" t="s">
+      <c r="L15" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="M15" s="145"/>
+      <c r="M15" s="131"/>
       <c r="N15" s="125" t="s">
         <v>5</v>
       </c>
@@ -12434,10 +12432,10 @@
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
       <c r="B16" s="32"/>
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="145"/>
+      <c r="D16" s="131"/>
       <c r="E16" s="125"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -12445,10 +12443,10 @@
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
       <c r="K16" s="32"/>
-      <c r="L16" s="142" t="s">
+      <c r="L16" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="M16" s="145"/>
+      <c r="M16" s="131"/>
       <c r="N16" s="125"/>
       <c r="O16" s="32"/>
       <c r="P16" s="32"/>
@@ -12456,10 +12454,10 @@
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="32"/>
       <c r="B17" s="32"/>
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="145"/>
+      <c r="D17" s="131"/>
       <c r="E17" s="125"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -12467,10 +12465,10 @@
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
-      <c r="L17" s="142" t="s">
+      <c r="L17" s="130" t="s">
         <v>51</v>
       </c>
-      <c r="M17" s="145"/>
+      <c r="M17" s="131"/>
       <c r="N17" s="125"/>
       <c r="O17" s="32"/>
       <c r="P17" s="32"/>
@@ -12478,10 +12476,10 @@
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="32"/>
       <c r="B18" s="32"/>
-      <c r="C18" s="142" t="s">
+      <c r="C18" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="145"/>
+      <c r="D18" s="131"/>
       <c r="E18" s="125"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32"/>
@@ -12489,10 +12487,10 @@
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
       <c r="K18" s="32"/>
-      <c r="L18" s="142" t="s">
+      <c r="L18" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="M18" s="145"/>
+      <c r="M18" s="131"/>
       <c r="N18" s="125"/>
       <c r="O18" s="32"/>
       <c r="P18" s="32"/>
@@ -12500,10 +12498,10 @@
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="32"/>
       <c r="B19" s="32"/>
-      <c r="C19" s="142" t="s">
+      <c r="C19" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="145"/>
+      <c r="D19" s="131"/>
       <c r="E19" s="125"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
@@ -12511,10 +12509,10 @@
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
       <c r="K19" s="32"/>
-      <c r="L19" s="142" t="s">
+      <c r="L19" s="130" t="s">
         <v>65</v>
       </c>
-      <c r="M19" s="145"/>
+      <c r="M19" s="131"/>
       <c r="N19" s="125"/>
       <c r="O19" s="32"/>
       <c r="P19" s="32"/>
@@ -12522,10 +12520,10 @@
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="32"/>
       <c r="B20" s="32"/>
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="145"/>
+      <c r="D20" s="131"/>
       <c r="E20" s="125"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
@@ -12533,10 +12531,10 @@
       <c r="I20" s="32"/>
       <c r="J20" s="32"/>
       <c r="K20" s="32"/>
-      <c r="L20" s="142" t="s">
+      <c r="L20" s="130" t="s">
         <v>132</v>
       </c>
-      <c r="M20" s="145"/>
+      <c r="M20" s="131"/>
       <c r="N20" s="125"/>
       <c r="O20" s="32"/>
       <c r="P20" s="32"/>
@@ -12544,10 +12542,10 @@
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="32"/>
       <c r="B21" s="32"/>
-      <c r="C21" s="142" t="s">
+      <c r="C21" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="145"/>
+      <c r="D21" s="131"/>
       <c r="E21" s="125"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
@@ -12555,10 +12553,10 @@
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
       <c r="K21" s="32"/>
-      <c r="L21" s="142" t="s">
+      <c r="L21" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="M21" s="145"/>
+      <c r="M21" s="131"/>
       <c r="N21" s="125"/>
       <c r="O21" s="32"/>
       <c r="P21" s="32"/>
@@ -12566,10 +12564,10 @@
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="32"/>
       <c r="B22" s="32"/>
-      <c r="C22" s="142" t="s">
+      <c r="C22" s="130" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="145"/>
+      <c r="D22" s="131"/>
       <c r="E22" s="125"/>
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
@@ -12577,10 +12575,10 @@
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
-      <c r="L22" s="142" t="s">
+      <c r="L22" s="130" t="s">
         <v>105</v>
       </c>
-      <c r="M22" s="145"/>
+      <c r="M22" s="131"/>
       <c r="N22" s="125"/>
       <c r="O22" s="32"/>
       <c r="P22" s="32"/>
@@ -12588,23 +12586,21 @@
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="32"/>
       <c r="B23" s="32"/>
-      <c r="C23" s="142" t="s">
+      <c r="C23" s="130" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="145"/>
-      <c r="E23" s="125" t="s">
-        <v>134</v>
-      </c>
+      <c r="D23" s="131"/>
+      <c r="E23" s="125"/>
       <c r="F23" s="32"/>
       <c r="G23" s="32"/>
       <c r="H23" s="32"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
       <c r="K23" s="32"/>
-      <c r="L23" s="142" t="s">
+      <c r="L23" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="M23" s="145"/>
+      <c r="M23" s="131"/>
       <c r="N23" s="125"/>
       <c r="O23" s="32"/>
       <c r="P23" s="32"/>
@@ -12728,6 +12724,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="L13:M13"/>
@@ -12740,27 +12757,6 @@
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="L22:M22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:O6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -12837,44 +12833,44 @@
     </row>
     <row r="2" spans="1:39" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A2" s="32"/>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="147" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
-      <c r="S2" s="129"/>
-      <c r="T2" s="129"/>
-      <c r="U2" s="129"/>
-      <c r="V2" s="129"/>
-      <c r="W2" s="129"/>
-      <c r="X2" s="129"/>
-      <c r="Y2" s="129"/>
-      <c r="Z2" s="129"/>
-      <c r="AA2" s="129"/>
-      <c r="AB2" s="129"/>
-      <c r="AC2" s="129"/>
-      <c r="AD2" s="129"/>
-      <c r="AE2" s="129"/>
-      <c r="AF2" s="129"/>
-      <c r="AG2" s="129"/>
-      <c r="AH2" s="129"/>
-      <c r="AI2" s="129"/>
-      <c r="AJ2" s="129"/>
-      <c r="AK2" s="129"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="147"/>
+      <c r="T2" s="147"/>
+      <c r="U2" s="147"/>
+      <c r="V2" s="147"/>
+      <c r="W2" s="147"/>
+      <c r="X2" s="147"/>
+      <c r="Y2" s="147"/>
+      <c r="Z2" s="147"/>
+      <c r="AA2" s="147"/>
+      <c r="AB2" s="147"/>
+      <c r="AC2" s="147"/>
+      <c r="AD2" s="147"/>
+      <c r="AE2" s="147"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="147"/>
+      <c r="AH2" s="147"/>
+      <c r="AI2" s="147"/>
+      <c r="AJ2" s="147"/>
+      <c r="AK2" s="147"/>
       <c r="AL2" s="32"/>
       <c r="AM2" s="36"/>
     </row>
@@ -12963,10 +12959,10 @@
     <row r="5" spans="1:39" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="32"/>
       <c r="B5" s="33"/>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="127"/>
+      <c r="D5" s="138"/>
       <c r="E5" s="40"/>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
@@ -12997,10 +12993,10 @@
       <c r="AF5" s="34"/>
       <c r="AG5" s="32"/>
       <c r="AH5" s="32"/>
-      <c r="AI5" s="126" t="s">
+      <c r="AI5" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="AJ5" s="127"/>
+      <c r="AJ5" s="138"/>
       <c r="AK5" s="35"/>
       <c r="AL5" s="32"/>
       <c r="AM5" s="36"/>
@@ -13061,10 +13057,10 @@
       <c r="D7" s="46"/>
       <c r="E7" s="47"/>
       <c r="F7" s="32"/>
-      <c r="G7" s="126" t="s">
+      <c r="G7" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="H7" s="127"/>
+      <c r="H7" s="138"/>
       <c r="I7" s="40"/>
       <c r="J7" s="32"/>
       <c r="K7" s="32"/>
@@ -13087,10 +13083,10 @@
       <c r="AB7" s="34"/>
       <c r="AC7" s="32"/>
       <c r="AD7" s="32"/>
-      <c r="AE7" s="126" t="s">
+      <c r="AE7" s="137" t="s">
         <v>117</v>
       </c>
-      <c r="AF7" s="127"/>
+      <c r="AF7" s="138"/>
       <c r="AG7" s="32"/>
       <c r="AH7" s="32"/>
       <c r="AI7" s="45"/>
@@ -13249,10 +13245,10 @@
       <c r="H11" s="34"/>
       <c r="I11" s="64"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="126" t="s">
+      <c r="K11" s="137" t="s">
         <v>118</v>
       </c>
-      <c r="L11" s="127"/>
+      <c r="L11" s="138"/>
       <c r="M11" s="40"/>
       <c r="N11" s="32"/>
       <c r="O11" s="32"/>
@@ -13267,10 +13263,10 @@
       <c r="X11" s="34"/>
       <c r="Y11" s="34"/>
       <c r="Z11" s="32"/>
-      <c r="AA11" s="126" t="s">
+      <c r="AA11" s="137" t="s">
         <v>118</v>
       </c>
-      <c r="AB11" s="127"/>
+      <c r="AB11" s="138"/>
       <c r="AC11" s="32"/>
       <c r="AD11" s="57"/>
       <c r="AE11" s="32"/>
@@ -13394,14 +13390,14 @@
       <c r="N14" s="32"/>
       <c r="O14" s="32"/>
       <c r="P14" s="34"/>
-      <c r="Q14" s="131" t="s">
+      <c r="Q14" s="140" t="s">
         <v>119</v>
       </c>
-      <c r="R14" s="132"/>
-      <c r="S14" s="132"/>
-      <c r="T14" s="132"/>
-      <c r="U14" s="132"/>
-      <c r="V14" s="133"/>
+      <c r="R14" s="141"/>
+      <c r="S14" s="141"/>
+      <c r="T14" s="141"/>
+      <c r="U14" s="141"/>
+      <c r="V14" s="142"/>
       <c r="W14" s="32"/>
       <c r="X14" s="34"/>
       <c r="Y14" s="34"/>
@@ -13441,12 +13437,12 @@
       <c r="N15" s="32"/>
       <c r="O15" s="32"/>
       <c r="P15" s="34"/>
-      <c r="Q15" s="134"/>
-      <c r="R15" s="135"/>
-      <c r="S15" s="135"/>
-      <c r="T15" s="135"/>
-      <c r="U15" s="135"/>
-      <c r="V15" s="136"/>
+      <c r="Q15" s="143"/>
+      <c r="R15" s="144"/>
+      <c r="S15" s="144"/>
+      <c r="T15" s="144"/>
+      <c r="U15" s="144"/>
+      <c r="V15" s="145"/>
       <c r="W15" s="32"/>
       <c r="X15" s="34"/>
       <c r="Y15" s="34"/>
@@ -13486,12 +13482,12 @@
       <c r="N16" s="32"/>
       <c r="O16" s="32"/>
       <c r="P16" s="34"/>
-      <c r="Q16" s="134"/>
-      <c r="R16" s="135"/>
-      <c r="S16" s="135"/>
-      <c r="T16" s="135"/>
-      <c r="U16" s="135"/>
-      <c r="V16" s="136"/>
+      <c r="Q16" s="143"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="144"/>
+      <c r="T16" s="144"/>
+      <c r="U16" s="144"/>
+      <c r="V16" s="145"/>
       <c r="W16" s="32"/>
       <c r="X16" s="34"/>
       <c r="Y16" s="34"/>
@@ -13574,20 +13570,20 @@
       <c r="L18" s="34"/>
       <c r="M18" s="64"/>
       <c r="N18" s="32"/>
-      <c r="O18" s="126" t="s">
+      <c r="O18" s="137" t="s">
         <v>120</v>
       </c>
-      <c r="P18" s="127"/>
+      <c r="P18" s="138"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="32"/>
       <c r="U18" s="34"/>
       <c r="V18" s="32"/>
-      <c r="W18" s="126" t="s">
+      <c r="W18" s="137" t="s">
         <v>120</v>
       </c>
-      <c r="X18" s="127"/>
+      <c r="X18" s="138"/>
       <c r="Y18" s="32"/>
       <c r="Z18" s="57"/>
       <c r="AA18" s="32"/>
@@ -13676,10 +13672,10 @@
       <c r="P20" s="46"/>
       <c r="Q20" s="47"/>
       <c r="R20" s="32"/>
-      <c r="S20" s="126" t="s">
+      <c r="S20" s="137" t="s">
         <v>121</v>
       </c>
-      <c r="T20" s="127"/>
+      <c r="T20" s="138"/>
       <c r="U20" s="34"/>
       <c r="V20" s="32"/>
       <c r="W20" s="45"/>
@@ -13903,8 +13899,8 @@
       <c r="P25" s="34"/>
       <c r="Q25" s="75"/>
       <c r="R25" s="32"/>
-      <c r="S25" s="128"/>
-      <c r="T25" s="128"/>
+      <c r="S25" s="146"/>
+      <c r="T25" s="146"/>
       <c r="U25" s="34"/>
       <c r="V25" s="77"/>
       <c r="W25" s="32"/>
@@ -13948,10 +13944,10 @@
       <c r="P26" s="34"/>
       <c r="Q26" s="75"/>
       <c r="R26" s="32"/>
-      <c r="S26" s="126" t="s">
+      <c r="S26" s="137" t="s">
         <v>122</v>
       </c>
-      <c r="T26" s="127"/>
+      <c r="T26" s="138"/>
       <c r="U26" s="34"/>
       <c r="V26" s="77"/>
       <c r="W26" s="32"/>
@@ -14179,10 +14175,10 @@
       <c r="P31" s="34"/>
       <c r="Q31" s="34"/>
       <c r="R31" s="32"/>
-      <c r="S31" s="126" t="s">
+      <c r="S31" s="137" t="s">
         <v>123</v>
       </c>
-      <c r="T31" s="127"/>
+      <c r="T31" s="138"/>
       <c r="U31" s="34"/>
       <c r="V31" s="32"/>
       <c r="W31" s="32"/>
@@ -14226,8 +14222,8 @@
       <c r="P32" s="34"/>
       <c r="Q32" s="34"/>
       <c r="R32" s="32"/>
-      <c r="S32" s="130"/>
-      <c r="T32" s="130"/>
+      <c r="S32" s="139"/>
+      <c r="T32" s="139"/>
       <c r="U32" s="34"/>
       <c r="V32" s="32"/>
       <c r="W32" s="32"/>
@@ -14795,11 +14791,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="Q14:V14"/>
-    <mergeCell ref="Q15:V16"/>
     <mergeCell ref="O18:P18"/>
     <mergeCell ref="W18:X18"/>
     <mergeCell ref="S20:T20"/>
@@ -14811,6 +14802,11 @@
     <mergeCell ref="AE7:AF7"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="Q14:V14"/>
+    <mergeCell ref="Q15:V16"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
